--- a/Alevia/MIRALEDO_Analiza_Ambalaje_ALEVIA.xlsx
+++ b/Alevia/MIRALEDO_Analiza_Ambalaje_ALEVIA.xlsx
@@ -1956,7 +1956,7 @@
       </c>
       <c r="C21" s="130" t="inlineStr">
         <is>
-          <t>365 produse pe alevia.ro (28.10.2026); 46 unitati de ambalaj identificate pana acum</t>
+          <t>365 produse pe alevia.ro (28.10.2026); 40 unitati de ambalaj identificate pana acum</t>
         </is>
       </c>
       <c r="D21" s="131" t="n"/>
@@ -2080,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N60"/>
+  <dimension ref="B2:N54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="3" customWidth="1" style="128" min="1" max="1"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="C7" s="133" t="inlineStr">
         <is>
-          <t>Blister(e) 30 comprimate masticabile (in cutie)</t>
+          <t>Blister comprimate masticabile (in cutie)</t>
         </is>
       </c>
       <c r="D7" s="133" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="F7" s="133" t="inlineStr">
         <is>
-          <t>Vitamina C cu pulpă de măceșe cu stevie Blister 30 comprimate masticabile</t>
+          <t>Propolis Vitamina C cu Echinacea Blister 20 comprimate masticabile; Vitamina C cu pulpă de măceșe cu stevie Blister 30 comprimate masticabile</t>
         </is>
       </c>
       <c r="G7" s="132" t="n"/>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="C8" s="133" t="inlineStr">
         <is>
-          <t>Blister(e) 20 comprimate (in cutie)</t>
+          <t>Blister comprimate (in cutie)</t>
         </is>
       </c>
       <c r="D8" s="133" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="F8" s="133" t="inlineStr">
         <is>
-          <t>Silfide Complex de slăbit forte Blister 20 comprimate</t>
+          <t>Montant Manșon 10 comprimate; Silfide Complex de slăbit forte Blister 20 comprimate</t>
         </is>
       </c>
       <c r="G8" s="132" t="n"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="C9" s="133" t="inlineStr">
         <is>
-          <t>Blister(e) 20 comprimate masticabile (in cutie)</t>
+          <t>Ambalaj interior capsule moi in cutie (blister sau flacon, de confirmat)</t>
         </is>
       </c>
       <c r="D9" s="133" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="F9" s="133" t="inlineStr">
         <is>
-          <t>Propolis Vitamina C cu Echinacea Blister 20 comprimate masticabile</t>
+          <t>Lecitina 1200mg 30 capsule moi; Omega 3 6 9 40 capsule moi; Omega 3 Forte 30 capsule moi; Silymarin Milk thistle 1000mg 30 capsule moi; Ulei de pește Omega 3 30 capsule moi</t>
         </is>
       </c>
       <c r="G9" s="132" t="n"/>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="C10" s="133" t="inlineStr">
         <is>
-          <t>Flacon 200 comprimate + capac</t>
+          <t>Ambalaj interior capsule vegetale in cutie (blister sau flacon, de confirmat)</t>
         </is>
       </c>
       <c r="D10" s="133" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E10" s="133" t="inlineStr">
         <is>
-          <t>Alb (flacon si capac, din poza)</t>
+          <t>De confirmat</t>
         </is>
       </c>
       <c r="F10" s="133" t="inlineStr">
         <is>
-          <t>Spirulină 500mg 200 comprimate</t>
+          <t>5-HTP plus 30 capsule vegetale; Adaptonic 20 capsule vegetale; Adaptonic Pachet 20+20 capsule vegetale; Articlar Colagen 30 capsule vegetale; Coenzima Q10 120mg 40 capsule vegetale; Coenzima Q10 200mg Intensiv 30 capsule vegetale; Coenzima Q10 60mg 30 capsule vegetale; Coenzima Q10 Complex 30 capsule vegetale; Detenso Calm 20 capsule vegetale; Detenso Somn 30 capsule vegetale; Detoxi complet 30 capsule vegetale; Femena Meno 30 capsule vegetale; Femena Meno Pachet 30+30 capsule vegetale; Femena Osteo 30 capsule vegetale; Ginkgo biloba cu Magneziu 60 capsule vegetale; Magne 5 30 capsule vegetale; Memo Clar 60 capsule vegetale; Neuro Clar 60 capsule vegetale; Nutrinergic 30 capsule vegetale; Nutrinergic Pachet 30+30 capsule vegetale; Păr și unghii 60 capsule vegetale; Păr și Unghii Pachet 60+60 capsule vegetale; Resveratrol sincro 30 capsule vegetale; Silfide Complex de slăbit forte + Fucoidan 60 capsule vegetale; Silfide Complex de slăbit forte + Fucoidan Pachet 60+60 capsule vegetale</t>
         </is>
       </c>
       <c r="G10" s="132" t="n"/>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="C11" s="133" t="inlineStr">
         <is>
-          <t>Flacon 120 capsule moi + capac</t>
+          <t>Ambalaj interior comprimate in cutie (blister sau flacon, de confirmat)</t>
         </is>
       </c>
       <c r="D11" s="133" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="E11" s="133" t="inlineStr">
         <is>
-          <t>Alb (flacon si capac, din poza)</t>
+          <t>De confirmat</t>
         </is>
       </c>
       <c r="F11" s="133" t="inlineStr">
         <is>
-          <t>Ulei de somon Omega 3 120 capsule moi; Ulei de pește Omega 3 120 capsule moi; Silymarin Milk thistle 1000mg 120 capsule moi</t>
+          <t>Antistres 30 comprimate; Articlar forte 60 comprimate; Articlar Forte Pachet 60+60 comprimate; Atusin 20 comprimate; Calciu D3 masticabil 30 comprimate; Colesterol control 60 comprimate; Complex B forte 100 comprimate; Complex menopauză 30 comprimate; Control diab 60 comprimate; Curcumin 95% curcuminoide 60 comprimate; Curcumin 95% Curcuminoide Pachet 60 + 60 comprimate; Heparepar 30 comprimate; Imunio 30 comprimate; Masculin Potent 30 comprimate; Masculin Potent 30 comprimate + Ginseng siberian 30 capsule vegetale; Memorie și concentrare 30 comprimate; Montant 30 comprimate; Montant Pachet 30+30 comprimate; Optimicin 20 comprimate; Silfide Complex de slăbit forte 100 comprimate; Silfide Complex de slăbit forte 100 comprimate + Ceai de slăbit 30 plicuri; Silfide Detox 30 comprimate; Silimarină 150mg 50 comprimate; Silimarină 300mg 50 comprimate; Silimarină 300mg Pachet 50+50 comprimate; Stres Formula 30 comprimate; Vitamine și multiminerale 30 comprimate</t>
         </is>
       </c>
       <c r="G11" s="132" t="n"/>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="C12" s="133" t="inlineStr">
         <is>
-          <t>Flacon 120 capsule vegetale + capac</t>
+          <t>Ambalaj interior comprimate masticabile in cutie (blister sau flacon, de confirmat)</t>
         </is>
       </c>
       <c r="D12" s="133" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="E12" s="133" t="inlineStr">
         <is>
-          <t>Alb (flacon si capac, din poza)</t>
+          <t>De confirmat</t>
         </is>
       </c>
       <c r="F12" s="133" t="inlineStr">
         <is>
-          <t>Vitamina C cu Zn și D3 1000mg 120 capsule vegetale; Vitamina D3 Optim 2000UI 120 capsule vegetale; Vitamina C 1000mg 120 capsule vegetale; Articlar Colagen 120 capsule vegetale; D3 + K2 Forte 120 capsule vegetale; Magneziu 375mg B6 120 capsule vegetale; Zinc Optim 25mg 120 capsule vegetale; Magneziu Bisglicinat 120 capsule vegetale</t>
+          <t>Complex gastric 30 comprimate masticabile; Florisept 20 comprimate masticabile; Propolis C-tare 30 comprimate masticabile; Propolis Vitamina C cu Echinacea și stevie 40 comprimate masticabile</t>
         </is>
       </c>
       <c r="G12" s="132" t="n"/>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="C13" s="133" t="inlineStr">
         <is>
-          <t>Flacon 120 comprimate + capac</t>
+          <t>Flacon capsule/comprimate + capac (eticheta 215x57 mm)</t>
         </is>
       </c>
       <c r="D13" s="133" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="F13" s="133" t="inlineStr">
         <is>
-          <t>Maca Pachet 120+120 comprimate; Vitamina B12 Optim 1000µg 120 comprimate; Maca 120 comprimate</t>
+          <t>Articlar Colagen 120 capsule vegetale; D3 + K2 Forte 120 capsule vegetale; Magneziu Bisglicinat 120 capsule vegetale; Magtein® 90 capsule vegetale; Seleniu Natural 200µg 120 comprimate filmate; Silymarin Milk thistle 1000mg 120 capsule moi; Ulei de pește Omega 3 120 capsule moi; Ulei de somon Omega 3 120 capsule moi; Vitamina B12 Optim 1000µg 120 comprimate; Vitamina C 1000mg 120 capsule vegetale; Vitamina C cu Zn și D3 1000mg 120 capsule vegetale</t>
         </is>
       </c>
       <c r="G13" s="132" t="n"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="C14" s="133" t="inlineStr">
         <is>
-          <t>Flacon 120 comprimate filmate + capac</t>
+          <t>Flacon capsule/comprimate + capac (eticheta 180x68 mm)</t>
         </is>
       </c>
       <c r="D14" s="133" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="F14" s="133" t="inlineStr">
         <is>
-          <t>Seleniu Natural 200µg 120 comprimate filmate</t>
+          <t>Ca+D3 60 comprimate; Calciu Magneziu Zinc 100 comprimate; CaMgZn + Vitamina C 60 comprimate; Coenzima Q10 60mg 60 capsule vegetale; Coenzima Q10 cu Catină 60 comprimate; Ginkgo biloba 100mg 60 comprimate; Ginkgo biloba 100mg Pachet 60+60 comprimate; Lecitină 1200mg 60 capsule moi; Magneziu 375mg B6 120 capsule vegetale; Omega 3 6 9 60 capsule moi; Omega 3 6 9 Pachet 60+60 capsule moi; Silimarină 150mg 100 comprimate; Silimarină 300mg 100 comprimate; Silymarin Milk thistle 1000mg 60 capsule moi; Spirulină 500mg 200 comprimate; Spirulină Bio 1000mg 100 comprimate; Spirulină Bio 1000mg Pachet 100+100 comprimate; Ulei de pește Omega 3 70 capsule moi; Ulei de somon Omega 3 60 capsule moi; Vitamina D3 Optim 2000UI 120 capsule vegetale; Zinc Optim 25mg 120 capsule vegetale</t>
         </is>
       </c>
       <c r="G14" s="132" t="n"/>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C15" s="133" t="inlineStr">
         <is>
-          <t>Flacon 100 comprimate + capac</t>
+          <t>Flacon capsule/comprimate + capac (eticheta 169x58,5 mm)</t>
         </is>
       </c>
       <c r="D15" s="133" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="F15" s="133" t="inlineStr">
         <is>
-          <t>Spirulină Bio 1000mg 100 comprimate; Calciu Magneziu Zinc 100 comprimate; Zaharină 100 comprimate; Silimarină 300mg 100 comprimate; Silimarină 150mg 100 comprimate; Spirulină Bio 1000mg Pachet 100+100 comprimate</t>
+          <t>Anghinare 60 comprimate; Anghinare Pachet 60+60 comprimate; Ashwagandha KSM-66® 600mg 30 capsule vegetale; Astaxanthin 6mg 30 capsule vegetale; Berberină Duo 60 capsule vegetale; Berberină Momordica Gluco Suport 30 capsule vegetale; Ca-Mg-Zn Vitamineral 60 comprimate; Calciu citrat Vitamina D3 30 capsule vegetale; Chimen Negru 500mg 30 capsule moi; Coenzima Q10 120mg 30 capsule vegetale; Coenzima Q10 120mg Pachet 30+30 capsule vegetale; D3 + K2 30 capsule vegetale; D3 + K2 Forte 30 capsule vegetale; EnzimDigest 30 capsule vegetale; Fier lipozomal 30 capsule vegetale; L-Arginină 60 capsule vegetale; Maca 120 comprimate; Maca Pachet 120+120 comprimate; Magneziu 375mg 30 capsule vegetale; Magneziu Bisglicinat 60 capsule vegetale; Magneziu Bisglicinat Forte 30 capsule vegetale; Magneziu Bisglicinat Somn 30 capsule vegetale; Magneziu citrat 30 capsule vegetale; Melatonină 3mg 30 capsule vegetale; Melatonină 5mg 30 capsule vegetale; MSM Optim 1000mg 30 comprimate; ProstatoSan 30 capsule vegetale; Quercetin cu Zn și D3 30 capsule vegetale; Quercetin cu Zn și D3 Pachet 30+30 capsule vegetale; Rhodiola 60 comprimate; Rhodiola Pachet 60+60 comprimate; Spirulină Bio 1000mg 45 comprimate; Tămâie 500mg Boswellia serrata 60 capsule vegetale; Vitamina C 1000mg 30 capsule vegetale; Vitamina C cu Zn și D3 1000mg 30 capsule vegetale; Vitamina C Lipozomală 30 capsule vegetale; Zinc bisglicinat 30 capsule vegetale</t>
         </is>
       </c>
       <c r="G15" s="132" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="C16" s="133" t="inlineStr">
         <is>
-          <t>Flacon 90 capsule vegetale + capac</t>
+          <t>Flacon capsule/comprimate + capac (eticheta 140x46 mm)</t>
         </is>
       </c>
       <c r="D16" s="133" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="F16" s="133" t="inlineStr">
         <is>
-          <t>Magtein® 90 capsule vegetale</t>
+          <t>Calciu lactic 30 comprimate; Calciu lactic 60 comprimate; Calciu Magneziu D 30 comprimate; Calciu Magneziu D Pachet 30+30 comprimate; Calciu Magneziu Zinc 40 comprimate; Calciu Vitamina D3 40 comprimate; Complex B 30 comprimate; Magneziu Vitamina B6 30 comprimate; Seleniu Natural 200µg 30 comprimate filmate; Urifin 30 comprimate; Urifin 30 comprimate + Urifin Ceai 20 plicuri; Urifin Pachet 30+30 comprimate; Vitamina B12 Optim 1000µg 30 comprimate; Vitamina C 180mg 20 comprimate masticabile; Vitamina C 180mg 60 comprimate masticabile; Vitamina D3 Forte 5000UI 30 comprimate; Vitamina D3 Optim 2000UI 30 capsule vegetale; Vitamine și minerale esențiale 30 comprimate; Zaharină 100 comprimate; Zinc Optim 25mg 30 capsule vegetale</t>
         </is>
       </c>
       <c r="G16" s="132" t="n"/>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="C17" s="133" t="inlineStr">
         <is>
-          <t>Flacon 70 capsule moi + capac</t>
+          <t>Flacon capsule/comprimate + capac (eticheta 99x14 mm)</t>
         </is>
       </c>
       <c r="D17" s="133" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="F17" s="133" t="inlineStr">
         <is>
-          <t>Ulei de pește Omega 3 70 capsule moi</t>
+          <t>Bomboane cu mentă 60 comprimate masticabile</t>
         </is>
       </c>
       <c r="G17" s="132" t="n"/>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="C18" s="133" t="inlineStr">
         <is>
-          <t>Flacon 60 capsule moi + capac</t>
+          <t>Flacon brun capsule/comprimate + capac (eticheta 169x58,5 mm)</t>
         </is>
       </c>
       <c r="D18" s="133" t="inlineStr">
@@ -2687,12 +2687,12 @@
       </c>
       <c r="E18" s="133" t="inlineStr">
         <is>
-          <t>Alb (flacon si capac, din poza)</t>
+          <t>Brun (flacon), maro (capac), din poza</t>
         </is>
       </c>
       <c r="F18" s="133" t="inlineStr">
         <is>
-          <t>Ulei de somon Omega 3 60 capsule moi; Lecitină 1200mg 60 capsule moi; Omega 3 6 9 Pachet 60+60 capsule moi; Omega 3 6 9 60 capsule moi; Silymarin Milk thistle 1000mg 60 capsule moi</t>
+          <t>Ginkana Circulație 30 capsule vegetale; Ginkana Memorie 30 capsule vegetale; Ginkana Memorie 30+30 capsule vegetale</t>
         </is>
       </c>
       <c r="G18" s="132" t="n"/>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="C19" s="133" t="inlineStr">
         <is>
-          <t>Flacon 60 capsule vegetale + capac</t>
+          <t>Flacon brun capsule/comprimate + capac (eticheta 140x46 mm)</t>
         </is>
       </c>
       <c r="D19" s="133" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="E19" s="133" t="inlineStr">
         <is>
-          <t>Alb (flacon si capac, din poza)</t>
+          <t>Brun (flacon), maro (capac), din poza</t>
         </is>
       </c>
       <c r="F19" s="133" t="inlineStr">
         <is>
-          <t>Tămâie 500mg Boswellia serrata 60 capsule vegetale; L-Arginină 60 capsule vegetale; Berberină Duo 60 capsule vegetale; Coenzima Q10 60mg 60 capsule vegetale; Magneziu Bisglicinat 60 capsule vegetale</t>
+          <t>Ginkana Ginkgo biloba 120mg 30 comprimate; Ginkana Ginkgo biloba 120mg Pachet 30+30 comprimate; Ginkana Ginkgo biloba 40mg 30 comprimate; Ginkana Ginkgo biloba 40mg Pachet 30+30 comprimate; Ginkana Ginkgo biloba 80mg forte 30 comprimate; Ginkana Ginkgo biloba 80mg forte Pachet 30+30 comprimate; Ginseng 30 comprimate; Ginseng Pachet 30+30 comprimate; Ginseng siberian 30 capsule vegetale; Ginseng siberian Pachet 30+30 capsule vegetale; Masculin Potent 30 comprimate + Ginseng siberian 30 capsule vegetale; Spirulină 500mg 30 comprimate; Spirulină 500mg Pachet 30+30 comprimate</t>
         </is>
       </c>
       <c r="G19" s="132" t="n"/>
@@ -2767,22 +2767,22 @@
       </c>
       <c r="C20" s="133" t="inlineStr">
         <is>
-          <t>Flacon 60 comprimate + capac</t>
+          <t>Flacon 1000 ml + capac</t>
         </is>
       </c>
       <c r="D20" s="133" t="inlineStr">
         <is>
-          <t>De confirmat</t>
+          <t>1000 ml</t>
         </is>
       </c>
       <c r="E20" s="133" t="inlineStr">
         <is>
-          <t>Alb (flacon si capac, din poza)</t>
+          <t>Alb (din poza)</t>
         </is>
       </c>
       <c r="F20" s="133" t="inlineStr">
         <is>
-          <t>Ginkgo biloba 100mg Pachet 60+60 comprimate; Rhodiola Pachet 60+60 comprimate; Anghinare 60 comprimate; Calciu lactic 60 comprimate; Anghinare Pachet 60+60 comprimate; Ca-Mg-Zn Vitamineral 60 comprimate; Ca+D3 60 comprimate; CaMgZn + Vitamina C 60 comprimate; Ginkgo biloba 100mg 60 comprimate; Coenzima Q10 cu Catină 60 comprimate; Rhodiola 60 comprimate</t>
+          <t>Suc de Noni Tahitian Bio 1000ml; Suc ecologic de Aloe Vera 1000ml</t>
         </is>
       </c>
       <c r="G20" s="132" t="n"/>
@@ -2812,22 +2812,22 @@
       </c>
       <c r="C21" s="133" t="inlineStr">
         <is>
-          <t>Flacon 60 comprimate masticabile + capac</t>
+          <t>Flacon 150 ml + capac (plastic sau sticla, de confirmat)</t>
         </is>
       </c>
       <c r="D21" s="133" t="inlineStr">
         <is>
+          <t>150 ml</t>
+        </is>
+      </c>
+      <c r="E21" s="133" t="inlineStr">
+        <is>
           <t>De confirmat</t>
         </is>
       </c>
-      <c r="E21" s="133" t="inlineStr">
-        <is>
-          <t>Alb (flacon si capac, din poza)</t>
-        </is>
-      </c>
       <c r="F21" s="133" t="inlineStr">
         <is>
-          <t>Bomboane cu mentă 60 comprimate masticabile; Vitamina C 180mg 60 comprimate masticabile</t>
+          <t>Atusin Sirop 150ml; Dodino Sirop Atusin 150ml; Dodino Sirop Calciu și Vitamina D3 150ml; Dodino Sirop cu Magneziu și Complex B 150ml; Dodino Sirop de Propolis cu Echinacea 150ml; Dodino Sirop Memorie și Concentrare 150ml; Dodino Sirop Vermilin 150ml; Dodino Sirop Vitamine și Multiminerale 150ml; Gripalin Sirop 150ml; Sirop de muguri de pin și brad 150ml; Sirop de pătlagină 150ml; Sirop laxatin 150ml; Sirop pentru imunitate 150ml; Sirop pentru somn 150ml</t>
         </is>
       </c>
       <c r="G21" s="132" t="n"/>
@@ -2857,22 +2857,22 @@
       </c>
       <c r="C22" s="133" t="inlineStr">
         <is>
-          <t>Flacon 45 comprimate + capac</t>
+          <t>Flacon 20 ml + spray (plastic sau sticla, de confirmat)</t>
         </is>
       </c>
       <c r="D22" s="133" t="inlineStr">
         <is>
+          <t>20 ml</t>
+        </is>
+      </c>
+      <c r="E22" s="133" t="inlineStr">
+        <is>
           <t>De confirmat</t>
         </is>
       </c>
-      <c r="E22" s="133" t="inlineStr">
-        <is>
-          <t>Alb (flacon si capac, din poza)</t>
-        </is>
-      </c>
       <c r="F22" s="133" t="inlineStr">
         <is>
-          <t>Spirulină Bio 1000mg 45 comprimate</t>
+          <t>Propolis C-tare Spray 20ml</t>
         </is>
       </c>
       <c r="G22" s="132" t="n"/>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="C23" s="133" t="inlineStr">
         <is>
-          <t>Flacon 40 comprimate + capac</t>
+          <t>Plic monodoza pulbere solubila</t>
         </is>
       </c>
       <c r="D23" s="133" t="inlineStr">
@@ -2912,12 +2912,12 @@
       </c>
       <c r="E23" s="133" t="inlineStr">
         <is>
-          <t>Alb (flacon si capac, din poza)</t>
+          <t>De confirmat</t>
         </is>
       </c>
       <c r="F23" s="133" t="inlineStr">
         <is>
-          <t>Calciu Magneziu Zinc 40 comprimate; Calciu Vitamina D3 40 comprimate</t>
+          <t>Articlar HyaluCollagen Solubil 20 plicuri; Articlar HyaluCollagen Solubil 30 plicuri; Beauty HyaluCollagen Solubil 20 plicuri; Calciu 1200mg Vitamina D3 Solubil 20 plicuri; Calciu Magneziu Zinc D3 Solubil 20 plicuri; Electroliți Forte - Săruri de rehidratare Solubil 20 plicuri; Gripalin Natural Solubil 10 plicuri; Magneziu 300mg Solubil 20 plicuri; Urifin rapid Solubil 15 plicuri; Urifin Rapid Solubil 15 plicuri + Ceai Urifin 20 plicuri Pachet x 2; Vitamina C Naturală 1000mg Solubil 15 plicuri; Vitamine și minerale Forte Solubil 15 plicuri</t>
         </is>
       </c>
       <c r="G23" s="132" t="n"/>
@@ -2947,22 +2947,22 @@
       </c>
       <c r="C24" s="133" t="inlineStr">
         <is>
-          <t>Flacon 30 capsule moi + capac</t>
+          <t>Borcan 250 g + capac</t>
         </is>
       </c>
       <c r="D24" s="133" t="inlineStr">
         <is>
-          <t>De confirmat</t>
+          <t>250 g / 250 ml</t>
         </is>
       </c>
       <c r="E24" s="133" t="inlineStr">
         <is>
-          <t>Alb (flacon si capac, din poza)</t>
+          <t>Alb (borcan si capac, din poza)</t>
         </is>
       </c>
       <c r="F24" s="133" t="inlineStr">
         <is>
-          <t>Chimen Negru 500mg 30 capsule moi</t>
+          <t>Articlar Gel 250g; Balsam Puterea Calului cu chili 250g; Balsam Vigoarea Ursului Polar 250g; Cremă de Arnică 250 ml; Cremă de Gălbenele 250g; Gheara Diavolului Balsam 250g; Gheara Diavolului Canabis Gel 250g; Picioare Obosite Cremă 250g; Puterea Calului Canabis Gel 250g</t>
         </is>
       </c>
       <c r="G24" s="132" t="n"/>
@@ -2992,22 +2992,22 @@
       </c>
       <c r="C25" s="133" t="inlineStr">
         <is>
-          <t>Flacon 30 capsule vegetale + capac</t>
+          <t>Recipient pulbere 300 g + capac</t>
         </is>
       </c>
       <c r="D25" s="133" t="inlineStr">
         <is>
-          <t>De confirmat</t>
+          <t>300 g</t>
         </is>
       </c>
       <c r="E25" s="133" t="inlineStr">
         <is>
-          <t>Alb (flacon si capac, din poza)</t>
+          <t>Alb (din poza)</t>
         </is>
       </c>
       <c r="F25" s="133" t="inlineStr">
         <is>
-          <t>Vitamina D3 Optim 2000UI 30 capsule vegetale; D3 + K2 30 capsule vegetale; Vitamina C 1000mg 30 capsule vegetale; Fier lipozomal 30 capsule vegetale; Berberină Momordica Gluco Suport 30 capsule vegetale; Coenzima Q10 120mg Pachet 30+30 capsule vegetale; Zinc bisglicinat 30 capsule vegetale; ProstatoSan 30 capsule vegetale; Magneziu Bisglicinat Forte 30 capsule vegetale; D3 + K2 Forte 30 capsule vegetale; EnzimDigest 30 capsule vegetale; Melatonină 3mg 30 capsule vegetale; Calciu citrat Vitamina D3 30 capsule vegetale; Melatonină 5mg 30 capsule vegetale; Vitamina C cu Zn și D3 1000mg 30 capsule vegetale; Quercetin cu Zn și D3 Pachet 30+30 capsule vegetale; Vitamina C Lipozomală 30 capsule vegetale; Magneziu citrat 30 capsule vegetale; Zinc Optim 25mg 30 capsule vegetale; Magneziu 375mg 30 capsule vegetale; Quercetin cu Zn și D3 30 capsule vegetale; Coenzima Q10 120mg 30 capsule vegetale; Astaxanthin 6mg 30 capsule vegetale; Ashwagandha KSM-66® 600mg 30 capsule vegetale; Magneziu Bisglicinat Somn 30 capsule vegetale</t>
+          <t>Colagen Peptide 300g; Colagen Peptide cu Acid hialuronic și Vitamina C 300g</t>
         </is>
       </c>
       <c r="G25" s="132" t="n"/>
@@ -3037,22 +3037,22 @@
       </c>
       <c r="C26" s="133" t="inlineStr">
         <is>
-          <t>Flacon 30 comprimate + capac</t>
+          <t>Recipient pulbere 140 g + capac</t>
         </is>
       </c>
       <c r="D26" s="133" t="inlineStr">
         <is>
-          <t>De confirmat</t>
+          <t>140 g</t>
         </is>
       </c>
       <c r="E26" s="133" t="inlineStr">
         <is>
-          <t>Alb (flacon si capac, din poza)</t>
+          <t>Alb (din poza)</t>
         </is>
       </c>
       <c r="F26" s="133" t="inlineStr">
         <is>
-          <t>Magneziu Vitamina B6 30 comprimate; Vitamina D3 Forte 5000UI 30 comprimate; MSM Optim 1000mg 30 comprimate; Urifin Pachet 30+30 comprimate; Vitamina B12 Optim 1000µg 30 comprimate; Calciu Magneziu D Pachet 30+30 comprimate; Calciu lactic 30 comprimate; Calciu Magneziu D 30 comprimate; Complex B 30 comprimate; Vitamine și minerale esențiale 30 comprimate; Urifin 30 comprimate</t>
+          <t>Inulină 140g</t>
         </is>
       </c>
       <c r="G26" s="132" t="n"/>
@@ -3082,22 +3082,22 @@
       </c>
       <c r="C27" s="133" t="inlineStr">
         <is>
-          <t>Flacon 30 comprimate filmate + capac</t>
+          <t>Borcan 20 g + capac</t>
         </is>
       </c>
       <c r="D27" s="133" t="inlineStr">
         <is>
-          <t>De confirmat</t>
+          <t>20 g</t>
         </is>
       </c>
       <c r="E27" s="133" t="inlineStr">
         <is>
-          <t>Alb (flacon si capac, din poza)</t>
+          <t>Alb (din poza)</t>
         </is>
       </c>
       <c r="F27" s="133" t="inlineStr">
         <is>
-          <t>Seleniu Natural 200µg 30 comprimate filmate</t>
+          <t>Alifie chinezească 20g; Balsam Arnică 20g; Balsam călcâie 20g; Balsam Gălbenele 20g; Balsam Gălbenele și Tătăneasă 20g; Balsam Propolis 20g; Balsam Rostopască 20g; Balsam Tătăneasă 20g</t>
         </is>
       </c>
       <c r="G27" s="132" t="n"/>
@@ -3127,22 +3127,22 @@
       </c>
       <c r="C28" s="133" t="inlineStr">
         <is>
-          <t>Flacon 20 comprimate masticabile + capac</t>
+          <t>Tub 200 ml + capac</t>
         </is>
       </c>
       <c r="D28" s="133" t="inlineStr">
         <is>
-          <t>De confirmat</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="E28" s="133" t="inlineStr">
         <is>
-          <t>Alb (flacon si capac, din poza)</t>
+          <t>Alb (din poza)</t>
         </is>
       </c>
       <c r="F28" s="133" t="inlineStr">
         <is>
-          <t>Vitamina C 180mg 20 comprimate masticabile</t>
+          <t>Gel anticelulitic 200ml</t>
         </is>
       </c>
       <c r="G28" s="132" t="n"/>
@@ -3172,22 +3172,22 @@
       </c>
       <c r="C29" s="133" t="inlineStr">
         <is>
-          <t>Flacon 30 capsule vegetale + capac</t>
+          <t>Tub 150 ml + capac</t>
         </is>
       </c>
       <c r="D29" s="133" t="inlineStr">
         <is>
-          <t>De confirmat</t>
+          <t>150 ml</t>
         </is>
       </c>
       <c r="E29" s="133" t="inlineStr">
         <is>
-          <t>Brun (flacon), maro (capac), din poza</t>
+          <t>Alb (din poza)</t>
         </is>
       </c>
       <c r="F29" s="133" t="inlineStr">
         <is>
-          <t>Ginkana Memorie 30 capsule vegetale; Ginseng siberian Pachet 30+30 capsule vegetale; Ginkana Circulație 30 capsule vegetale; Ginseng siberian 30 capsule vegetale; Ginkana Memorie 30+30 capsule vegetale; Masculin Potent 30 comprimate + Ginseng siberian 30 capsule vegetale</t>
+          <t>Cremă antivergeturi 150ml</t>
         </is>
       </c>
       <c r="G29" s="132" t="n"/>
@@ -3217,22 +3217,22 @@
       </c>
       <c r="C30" s="133" t="inlineStr">
         <is>
-          <t>Flacon 30 comprimate + capac</t>
+          <t>Tub 50 ml + capac</t>
         </is>
       </c>
       <c r="D30" s="133" t="inlineStr">
         <is>
-          <t>De confirmat</t>
+          <t>50 ml</t>
         </is>
       </c>
       <c r="E30" s="133" t="inlineStr">
         <is>
-          <t>Brun (flacon), maro (capac), din poza</t>
+          <t>Alb (din poza)</t>
         </is>
       </c>
       <c r="F30" s="133" t="inlineStr">
         <is>
-          <t>Ginkana Ginkgo biloba 80mg forte Pachet 30+30 comprimate; Ginseng Pachet 30+30 comprimate; Ginkana Ginkgo biloba 40mg Pachet 30+30 comprimate; Spirulină 500mg Pachet 30+30 comprimate; Ginkana Ginkgo biloba 120mg Pachet 30+30 comprimate; Ginkana Ginkgo biloba 80mg forte 30 comprimate; Ginkana Ginkgo biloba 40mg 30 comprimate; Ginkana Ginkgo biloba 120mg 30 comprimate; Ginseng 30 comprimate; Spirulină 500mg 30 comprimate</t>
+          <t>Articlar Gel 50ml; Crema cu uree 15% 50ml; Cremă de mâini cu Gălbenele și Aloe vera 50ml; Gel înțepături insecte 50ml</t>
         </is>
       </c>
       <c r="G30" s="132" t="n"/>
@@ -3262,12 +3262,12 @@
       </c>
       <c r="C31" s="133" t="inlineStr">
         <is>
-          <t>Flacon 1000 ml + capac</t>
+          <t>Tub 20 ml + capac</t>
         </is>
       </c>
       <c r="D31" s="133" t="inlineStr">
         <is>
-          <t>1000 ml</t>
+          <t>20 ml</t>
         </is>
       </c>
       <c r="E31" s="133" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="F31" s="133" t="inlineStr">
         <is>
-          <t>Suc de Noni Tahitian Bio 1000ml; Suc ecologic de Aloe Vera 1000ml</t>
+          <t>Cremă Antiacneică 20 ml; Gel bătături 20ml</t>
         </is>
       </c>
       <c r="G31" s="132" t="n"/>
@@ -3307,12 +3307,12 @@
       </c>
       <c r="C32" s="133" t="inlineStr">
         <is>
-          <t>Flacon 20 ml + spray (in cutie)</t>
+          <t>Plic ceai (in cutie)</t>
         </is>
       </c>
       <c r="D32" s="133" t="inlineStr">
         <is>
-          <t>20 ml</t>
+          <t>De confirmat</t>
         </is>
       </c>
       <c r="E32" s="133" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="F32" s="133" t="inlineStr">
         <is>
-          <t>Propolis C-tare Spray 20ml</t>
+          <t>Atusin Ceai 20 plicuri; Ceai antigripol 40 plicuri; Ceai antistres 20 plicuri; Ceai colesterol 20 plicuri; Ceai cu afine 20 plicuri; Ceai cu mere și coacăze 20 plicuri; Ceai de crușin 20 plicuri; Ceai de ghimbir cu coajă de portocale 20 plicuri; Ceai de gălbenele 20 plicuri; Ceai de gălbenele 40 plicuri; Ceai de lavandă 20 plicuri; Ceai de mentă 20 plicuri; Ceai de mentă cu aromă de lămâie 20 plicuri; Ceai de mușețel 20 plicuri; Ceai de mușețel 40 plicuri; Ceai de slăbit 20 plicuri; Ceai de slăbit 40 plicuri; Ceai de soc 20 plicuri; Ceai de sunătoare 20 plicuri; Ceai de sunătoare 40 plicuri; Ceai de tei 20 plicuri; Ceai de tei 40 plicuri; Ceai de urzică 20 plicuri; Ceai digestiv 20 plicuri; Ceai diuretic 20 plicuri; Ceai fructe de pădure 20 plicuri; Ceai gastric 20 plicuri; Ceai Gripalin 20 plicuri; Ceai hepatic 20 plicuri; Ceai hepatic 40 plicuri; Ceai imunitate 20 plicuri; Ceai laxatin 20 plicuri; Ceai menopauză 20 plicuri; Ceai negru 20 plicuri; Ceai normalizarea glicemiei 20 plicuri; Ceai normalizarea glicemiei 40 plicuri; Ceai pentru articulații 20 plicuri; Ceai pentru prostată 20 plicuri; Ceai pentru somn 20 plicuri; Ceai pentru tensiune 20 plicuri; Ceai renal 20 plicuri; Ceai verde 20 plicuri; Complex de slăbit ceai cu ginseng și ananas 30 plicuri; Silfide Complex de slăbit forte 100 comprimate + Ceai de slăbit 30 plicuri; Urifin 30 comprimate + Urifin Ceai 20 plicuri; Urifin Rapid Solubil 15 plicuri + Ceai Urifin 20 plicuri Pachet x 2</t>
         </is>
       </c>
       <c r="G32" s="132" t="n"/>
@@ -3352,22 +3352,22 @@
       </c>
       <c r="C33" s="133" t="inlineStr">
         <is>
-          <t>Recipient pulbere 300 g + capac</t>
+          <t>Plic piramida ceai (in cutie)</t>
         </is>
       </c>
       <c r="D33" s="133" t="inlineStr">
         <is>
-          <t>300 g</t>
+          <t>De confirmat</t>
         </is>
       </c>
       <c r="E33" s="133" t="inlineStr">
         <is>
-          <t>Alb (din poza)</t>
+          <t>De confirmat</t>
         </is>
       </c>
       <c r="F33" s="133" t="inlineStr">
         <is>
-          <t>Colagen Peptide 300g; Colagen Peptide cu Acid hialuronic și Vitamina C 300g</t>
+          <t>TABIETURI Ceai de Fructe roșii 12 plicuri; TABIETURI Ceai de Mentă delicat 12 plicuri; TABIETURI Ceai de Merișor 12 plicuri; TABIETURI Ceai de Mușețel și citrice 12 plicuri; TABIETURI Ceai English breakfast 12 plicuri; TABIETURI Ceai Fruit melange 12 plicuri; TABIETURI Ceai Oriental condimentat 12 plicuri; TABIETURI Ceai Rooibos Creme brulee 12 plicuri; TABIETURI Ceai Verde cu aromă de Iasomie 12 plicuri</t>
         </is>
       </c>
       <c r="G33" s="132" t="n"/>
@@ -3397,22 +3397,22 @@
       </c>
       <c r="C34" s="133" t="inlineStr">
         <is>
-          <t>Borcan 250 g + capac</t>
+          <t>Punga interioara ceai vrac (in cutie, de confirmat)</t>
         </is>
       </c>
       <c r="D34" s="133" t="inlineStr">
         <is>
-          <t>250 g / 250 ml</t>
+          <t>40 / 50 / 70 g</t>
         </is>
       </c>
       <c r="E34" s="133" t="inlineStr">
         <is>
-          <t>Alb (borcan si capac, din poza)</t>
+          <t>De confirmat</t>
         </is>
       </c>
       <c r="F34" s="133" t="inlineStr">
         <is>
-          <t>Picioare Obosite Cremă 250g; Balsam Vigoarea Ursului Polar 250g; Gheara Diavolului Balsam 250g; Cremă de Gălbenele 250g; Cremă de Arnică 250 ml; Balsam Puterea Calului cu chili 250g; Articlar Gel 250g; Puterea Calului Canabis Gel 250g; Gheara Diavolului Canabis Gel 250g</t>
+          <t>Ceai de anason vrac 50g; Ceai de anghinare vrac 50g; Ceai de armurariu vrac 50g; Ceai de chimen vrac 50g; Ceai de coada calului vrac 50g; Ceai de coada șoricelului vrac 50g; Ceai de codițe de cireșe vrac 50g; Ceai de cătină vrac 50g; Ceai de echinacea vrac 50g; Ceai de fenicul vrac 50g; Ceai de ghimbir vrac 50g; Ceai de ghimpe vrac 50g; Ceai de gălbenele vrac 50g; Ceai de lemn-dulce vrac 40g; Ceai de mentă vrac 50g; Ceai de mușețel vrac 40g; Ceai de măceșe vrac 50g; Ceai de pufuliță cu flori mici vrac 50g; Ceai de păducel cu flori vrac 50g; Ceai de păpădie vrac 50g; Ceai de pătlagină vrac 50g; Ceai de roinița vrac 50g; Ceai de salvie vrac 50g; Ceai de senna vrac 50g; Ceai de slăbit vrac 50g; Ceai de sunătoare vrac 50g; Ceai de tei vrac 40g; Ceai detoxifiere vrac 50g; Ceai din mătase de porumb vrac 50g; Ceai hepatobiliar vrac 50g; Ceai normalizarea glicemiei vrac 50g; Ceai pentru fiere și rinichi vrac 50 g; Complex de slăbit cu ceai verde și lămâie vrac 70g; Gripalin Ceai vrac 50g</t>
         </is>
       </c>
       <c r="G34" s="132" t="n"/>
@@ -3442,22 +3442,22 @@
       </c>
       <c r="C35" s="133" t="inlineStr">
         <is>
-          <t>Recipient pulbere 140 g + capac</t>
+          <t>Punga ceai 35 g</t>
         </is>
       </c>
       <c r="D35" s="133" t="inlineStr">
         <is>
-          <t>140 g</t>
+          <t>35 g</t>
         </is>
       </c>
       <c r="E35" s="133" t="inlineStr">
         <is>
-          <t>Alb (din poza)</t>
+          <t>De confirmat</t>
         </is>
       </c>
       <c r="F35" s="133" t="inlineStr">
         <is>
-          <t>Inulină 140g</t>
+          <t>Ceai Fructe de pădure cu scorțișoară 35g; Ceai Rooibos cu vanilie 35g</t>
         </is>
       </c>
       <c r="G35" s="132" t="n"/>
@@ -3487,22 +3487,22 @@
       </c>
       <c r="C36" s="133" t="inlineStr">
         <is>
-          <t>Borcan 20 g + capac</t>
+          <t>Punga 1 kg</t>
         </is>
       </c>
       <c r="D36" s="133" t="inlineStr">
         <is>
-          <t>20 g</t>
+          <t>1 kg</t>
         </is>
       </c>
       <c r="E36" s="133" t="inlineStr">
         <is>
-          <t>Alb (din poza)</t>
+          <t>Transparenta + eticheta (din poza)</t>
         </is>
       </c>
       <c r="F36" s="133" t="inlineStr">
         <is>
-          <t>Balsam Gălbenele și Tătăneasă 20g; Alifie chinezească 20g; Balsam Propolis 20g; Balsam călcâie 20g; Balsam Rostopască 20g; Balsam Gălbenele 20g; Balsam Arnică 20g; Balsam Tătăneasă 20g</t>
+          <t>Goji 1kg; Merișor 1kg; Omega Mix 1kg; Seminte de In 1kg; Semințe de Chia 1kg; Vitamin Mix Merișor și Goji 1kg</t>
         </is>
       </c>
       <c r="G36" s="132" t="n"/>
@@ -3532,22 +3532,22 @@
       </c>
       <c r="C37" s="133" t="inlineStr">
         <is>
-          <t>Tub 200 ml + capac</t>
+          <t>Punga 500 g</t>
         </is>
       </c>
       <c r="D37" s="133" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>500 g</t>
         </is>
       </c>
       <c r="E37" s="133" t="inlineStr">
         <is>
-          <t>Alb (din poza)</t>
+          <t>Transparenta + eticheta (din poza)</t>
         </is>
       </c>
       <c r="F37" s="133" t="inlineStr">
         <is>
-          <t>Gel anticelulitic 200ml</t>
+          <t>Fulgi de Grâu 500g; Fulgi de Orz 500g; Fulgi de Ovăz 500g; Fulgi de Porumb 500g; Fulgi de Porumb fără zahăr 500g; Fulgi de Secară 500g; Goji 500g; Merișor 500g; Musli cereale și fructe uscate 500g; Musli mix 500g; Năut 500g; Omega Mix 500g; Sare roz de Himalaya Cristale neiodată 500g; Seminte de Chia 500g; Seminte de In 500g; Vitamin Mix Merisor și Goji 500g</t>
         </is>
       </c>
       <c r="G37" s="132" t="n"/>
@@ -3577,22 +3577,22 @@
       </c>
       <c r="C38" s="133" t="inlineStr">
         <is>
-          <t>Tub 150 ml + capac</t>
+          <t>Punga 250 g</t>
         </is>
       </c>
       <c r="D38" s="133" t="inlineStr">
         <is>
-          <t>150 ml</t>
+          <t>250 g</t>
         </is>
       </c>
       <c r="E38" s="133" t="inlineStr">
         <is>
-          <t>Alb (din poza)</t>
+          <t>Transparenta + eticheta (din poza)</t>
         </is>
       </c>
       <c r="F38" s="133" t="inlineStr">
         <is>
-          <t>Cremă antivergeturi 150ml</t>
+          <t>Caju crud 250g; Goji 250g; Merișor 250g; Migdale crude 250 g; Seminte Crude de Floarea Soarelui 250g; Semințe crude de Dovleac 250g; Tărâțe de Psyllium 250g</t>
         </is>
       </c>
       <c r="G38" s="132" t="n"/>
@@ -3622,22 +3622,22 @@
       </c>
       <c r="C39" s="133" t="inlineStr">
         <is>
-          <t>Tub 50 ml + capac</t>
+          <t>Punga 160 g</t>
         </is>
       </c>
       <c r="D39" s="133" t="inlineStr">
         <is>
-          <t>50 ml</t>
+          <t>160 g</t>
         </is>
       </c>
       <c r="E39" s="133" t="inlineStr">
         <is>
-          <t>Alb (din poza)</t>
+          <t>Transparenta + eticheta (din poza)</t>
         </is>
       </c>
       <c r="F39" s="133" t="inlineStr">
         <is>
-          <t>Gel înțepături insecte 50ml; Articlar Gel 50ml; Cremă de mâini cu Gălbenele și Aloe vera 50ml; Crema cu uree 15% 50ml</t>
+          <t>Seminte Crude de Floarea Soarelui 160g</t>
         </is>
       </c>
       <c r="G39" s="132" t="n"/>
@@ -3667,22 +3667,22 @@
       </c>
       <c r="C40" s="133" t="inlineStr">
         <is>
-          <t>Tub 20 ml + capac</t>
+          <t>Punga 150 g</t>
         </is>
       </c>
       <c r="D40" s="133" t="inlineStr">
         <is>
-          <t>20 ml</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="E40" s="133" t="inlineStr">
         <is>
-          <t>Alb (din poza)</t>
+          <t>Transparenta + eticheta (din poza)</t>
         </is>
       </c>
       <c r="F40" s="133" t="inlineStr">
         <is>
-          <t>Gel bătături 20ml; Cremă Antiacneică 20 ml</t>
+          <t>Arahide crude 150g; Mix Semințe de Floarea Soarelui și Dovleac 150g; Semințe crude de Dovleac 150g</t>
         </is>
       </c>
       <c r="G40" s="132" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="C41" s="133" t="inlineStr">
         <is>
-          <t>Punga 1 kg</t>
+          <t>Punga 140 g</t>
         </is>
       </c>
       <c r="D41" s="133" t="inlineStr">
         <is>
-          <t>1 kg</t>
+          <t>140 g</t>
         </is>
       </c>
       <c r="E41" s="133" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="F41" s="133" t="inlineStr">
         <is>
-          <t>Seminte de In 1kg; Merișor 1kg; Semințe de Chia 1kg; Omega Mix 1kg; Vitamin Mix Merișor și Goji 1kg; Goji 1kg</t>
+          <t>Migdale crude 140 g</t>
         </is>
       </c>
       <c r="G41" s="132" t="n"/>
@@ -3757,12 +3757,12 @@
       </c>
       <c r="C42" s="133" t="inlineStr">
         <is>
-          <t>Punga 500 g</t>
+          <t>Punga 130 g</t>
         </is>
       </c>
       <c r="D42" s="133" t="inlineStr">
         <is>
-          <t>500 g</t>
+          <t>130 g</t>
         </is>
       </c>
       <c r="E42" s="133" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="F42" s="133" t="inlineStr">
         <is>
-          <t>Seminte de Chia 500g; Fulgi de Ovăz 500g; Musli cereale și fructe uscate 500g; Sare roz de Himalaya Cristale neiodată 500g; Musli mix 500g; Seminte de In 500g; Fulgi de Porumb 500g; Fulgi de Porumb fără zahăr 500g; Omega Mix 500g; Fulgi de Secară 500g; Fulgi de Grâu 500g; Vitamin Mix Merisor și Goji 500g; Goji 500g; Năut 500g; Merișor 500g; Fulgi de Orz 500g</t>
+          <t>Fistic crud 130g; Mix Caju și Migdale 130g; Mix Fructe uscate și Nuci 130g; Omega Mix 130g; Semințe de In 130g; Stafide brune 130g</t>
         </is>
       </c>
       <c r="G42" s="132" t="n"/>
@@ -3802,12 +3802,12 @@
       </c>
       <c r="C43" s="133" t="inlineStr">
         <is>
-          <t>Punga 250 g</t>
+          <t>Punga 110 g</t>
         </is>
       </c>
       <c r="D43" s="133" t="inlineStr">
         <is>
-          <t>250 g</t>
+          <t>110 g</t>
         </is>
       </c>
       <c r="E43" s="133" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="F43" s="133" t="inlineStr">
         <is>
-          <t>Seminte Crude de Floarea Soarelui 250g; Migdale crude 250 g; Tărâțe de Psyllium 250g; Caju crud 250g; Merișor 250g; Semințe crude de Dovleac 250g; Goji 250g</t>
+          <t>Caju crud 110g; Merișor 110g; Vitamin Mix Merișor și Goji 110g</t>
         </is>
       </c>
       <c r="G43" s="132" t="n"/>
@@ -3847,12 +3847,12 @@
       </c>
       <c r="C44" s="133" t="inlineStr">
         <is>
-          <t>Punga 160 g</t>
+          <t>Punga 100 g</t>
         </is>
       </c>
       <c r="D44" s="133" t="inlineStr">
         <is>
-          <t>160 g</t>
+          <t>100 g</t>
         </is>
       </c>
       <c r="E44" s="133" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="F44" s="133" t="inlineStr">
         <is>
-          <t>Seminte Crude de Floarea Soarelui 160g</t>
+          <t>Goji 100g; Semințe de Chia 100g; Semințe de Susan 100g</t>
         </is>
       </c>
       <c r="G44" s="132" t="n"/>
@@ -3892,12 +3892,12 @@
       </c>
       <c r="C45" s="133" t="inlineStr">
         <is>
-          <t>Punga 150 g</t>
+          <t>Punga 85 g</t>
         </is>
       </c>
       <c r="D45" s="133" t="inlineStr">
         <is>
-          <t>150 g</t>
+          <t>85 g</t>
         </is>
       </c>
       <c r="E45" s="133" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="F45" s="133" t="inlineStr">
         <is>
-          <t>Mix Semințe de Floarea Soarelui și Dovleac 150g; Semințe crude de Dovleac 150g; Arahide crude 150g</t>
+          <t>Alune de pădure 85g</t>
         </is>
       </c>
       <c r="G45" s="132" t="n"/>
@@ -3937,22 +3937,22 @@
       </c>
       <c r="C46" s="133" t="inlineStr">
         <is>
-          <t>Punga 140 g</t>
+          <t>Rasnita 200 g (recipient + mecanism de macinare)</t>
         </is>
       </c>
       <c r="D46" s="133" t="inlineStr">
         <is>
-          <t>140 g</t>
+          <t>200 g</t>
         </is>
       </c>
       <c r="E46" s="133" t="inlineStr">
         <is>
-          <t>Transparenta + eticheta (din poza)</t>
+          <t>Transparent (recipient), negru (rasnita), din poza</t>
         </is>
       </c>
       <c r="F46" s="133" t="inlineStr">
         <is>
-          <t>Migdale crude 140 g</t>
+          <t>Sare roz de Himalaya Neiodată Râșniță 200g</t>
         </is>
       </c>
       <c r="G46" s="132" t="n"/>
@@ -3977,341 +3977,97 @@
       <c r="M46" s="138" t="n"/>
     </row>
     <row r="47" s="128">
-      <c r="B47" s="132" t="n">
-        <v>41</v>
-      </c>
-      <c r="C47" s="133" t="inlineStr">
-        <is>
-          <t>Punga 130 g</t>
-        </is>
-      </c>
-      <c r="D47" s="133" t="inlineStr">
-        <is>
-          <t>130 g</t>
-        </is>
-      </c>
-      <c r="E47" s="133" t="inlineStr">
-        <is>
-          <t>Transparenta + eticheta (din poza)</t>
-        </is>
-      </c>
-      <c r="F47" s="133" t="inlineStr">
-        <is>
-          <t>Semințe de In 130g; Omega Mix 130g; Stafide brune 130g; Mix Caju și Migdale 130g; Mix Fructe uscate și Nuci 130g; Fistic crud 130g</t>
-        </is>
-      </c>
+      <c r="B47" s="132" t="n"/>
+      <c r="C47" s="132" t="n"/>
+      <c r="D47" s="132" t="n"/>
+      <c r="E47" s="132" t="n"/>
+      <c r="F47" s="132" t="n"/>
       <c r="G47" s="132" t="n"/>
-      <c r="H47" s="134">
-        <f>IFERROR(INDIRECT("'"&amp;G47&amp;"'!E26"),"")</f>
-        <v/>
-      </c>
-      <c r="I47" s="135">
-        <f>IFERROR(INDIRECT("'"&amp;G47&amp;"'!E27"),"")</f>
-        <v/>
-      </c>
-      <c r="J47" s="136">
-        <f>IFERROR(INDIRECT("'"&amp;G47&amp;"'!E28"),"")</f>
-        <v/>
-      </c>
-      <c r="K47" s="137" t="n"/>
-      <c r="L47" s="137" t="inlineStr">
-        <is>
-          <t>In curs</t>
-        </is>
-      </c>
-      <c r="M47" s="138" t="n"/>
+      <c r="H47" s="132" t="n"/>
+      <c r="I47" s="132" t="n"/>
+      <c r="J47" s="132" t="n"/>
+      <c r="K47" s="132" t="n"/>
+      <c r="L47" s="132" t="n"/>
+      <c r="M47" s="132" t="n"/>
     </row>
     <row r="48" s="128">
-      <c r="B48" s="132" t="n">
-        <v>42</v>
-      </c>
-      <c r="C48" s="133" t="inlineStr">
-        <is>
-          <t>Punga 110 g</t>
-        </is>
-      </c>
-      <c r="D48" s="133" t="inlineStr">
-        <is>
-          <t>110 g</t>
-        </is>
-      </c>
-      <c r="E48" s="133" t="inlineStr">
-        <is>
-          <t>Transparenta + eticheta (din poza)</t>
-        </is>
-      </c>
-      <c r="F48" s="133" t="inlineStr">
-        <is>
-          <t>Caju crud 110g; Merișor 110g; Vitamin Mix Merișor și Goji 110g</t>
-        </is>
-      </c>
+      <c r="B48" s="132" t="n"/>
+      <c r="C48" s="132" t="n"/>
+      <c r="D48" s="132" t="n"/>
+      <c r="E48" s="132" t="n"/>
+      <c r="F48" s="132" t="n"/>
       <c r="G48" s="132" t="n"/>
-      <c r="H48" s="134">
-        <f>IFERROR(INDIRECT("'"&amp;G48&amp;"'!E26"),"")</f>
-        <v/>
-      </c>
-      <c r="I48" s="135">
-        <f>IFERROR(INDIRECT("'"&amp;G48&amp;"'!E27"),"")</f>
-        <v/>
-      </c>
-      <c r="J48" s="136">
-        <f>IFERROR(INDIRECT("'"&amp;G48&amp;"'!E28"),"")</f>
-        <v/>
-      </c>
-      <c r="K48" s="137" t="n"/>
-      <c r="L48" s="137" t="inlineStr">
-        <is>
-          <t>In curs</t>
-        </is>
-      </c>
-      <c r="M48" s="138" t="n"/>
-    </row>
-    <row r="49" s="128">
-      <c r="B49" s="132" t="n">
-        <v>43</v>
-      </c>
-      <c r="C49" s="133" t="inlineStr">
-        <is>
-          <t>Punga 100 g</t>
-        </is>
-      </c>
-      <c r="D49" s="133" t="inlineStr">
-        <is>
-          <t>100 g</t>
-        </is>
-      </c>
-      <c r="E49" s="133" t="inlineStr">
-        <is>
-          <t>Transparenta + eticheta (din poza)</t>
-        </is>
-      </c>
-      <c r="F49" s="133" t="inlineStr">
-        <is>
-          <t>Semințe de Chia 100g; Semințe de Susan 100g; Goji 100g</t>
-        </is>
-      </c>
-      <c r="G49" s="132" t="n"/>
-      <c r="H49" s="134">
-        <f>IFERROR(INDIRECT("'"&amp;G49&amp;"'!E26"),"")</f>
-        <v/>
-      </c>
-      <c r="I49" s="135">
-        <f>IFERROR(INDIRECT("'"&amp;G49&amp;"'!E27"),"")</f>
-        <v/>
-      </c>
-      <c r="J49" s="136">
-        <f>IFERROR(INDIRECT("'"&amp;G49&amp;"'!E28"),"")</f>
-        <v/>
-      </c>
-      <c r="K49" s="137" t="n"/>
-      <c r="L49" s="137" t="inlineStr">
-        <is>
-          <t>In curs</t>
-        </is>
-      </c>
-      <c r="M49" s="138" t="n"/>
-    </row>
-    <row r="50" s="128">
-      <c r="B50" s="132" t="n">
-        <v>44</v>
-      </c>
-      <c r="C50" s="133" t="inlineStr">
-        <is>
-          <t>Punga 85 g</t>
-        </is>
-      </c>
-      <c r="D50" s="133" t="inlineStr">
-        <is>
-          <t>85 g</t>
-        </is>
-      </c>
-      <c r="E50" s="133" t="inlineStr">
-        <is>
-          <t>Transparenta + eticheta (din poza)</t>
-        </is>
-      </c>
-      <c r="F50" s="133" t="inlineStr">
-        <is>
-          <t>Alune de pădure 85g</t>
-        </is>
-      </c>
-      <c r="G50" s="132" t="n"/>
-      <c r="H50" s="134">
-        <f>IFERROR(INDIRECT("'"&amp;G50&amp;"'!E26"),"")</f>
-        <v/>
-      </c>
-      <c r="I50" s="135">
-        <f>IFERROR(INDIRECT("'"&amp;G50&amp;"'!E27"),"")</f>
-        <v/>
-      </c>
-      <c r="J50" s="136">
-        <f>IFERROR(INDIRECT("'"&amp;G50&amp;"'!E28"),"")</f>
-        <v/>
-      </c>
-      <c r="K50" s="137" t="n"/>
-      <c r="L50" s="137" t="inlineStr">
-        <is>
-          <t>In curs</t>
-        </is>
-      </c>
-      <c r="M50" s="138" t="n"/>
-    </row>
-    <row r="51" s="128">
-      <c r="B51" s="132" t="n">
-        <v>45</v>
-      </c>
-      <c r="C51" s="133" t="inlineStr">
-        <is>
-          <t>Punga ceai 35 g</t>
-        </is>
-      </c>
-      <c r="D51" s="133" t="inlineStr">
-        <is>
-          <t>35 g</t>
-        </is>
-      </c>
-      <c r="E51" s="133" t="inlineStr">
-        <is>
-          <t>De confirmat</t>
-        </is>
-      </c>
-      <c r="F51" s="133" t="inlineStr">
-        <is>
-          <t>Ceai Rooibos cu vanilie 35g; Ceai Fructe de pădure cu scorțișoară 35g</t>
-        </is>
-      </c>
-      <c r="G51" s="132" t="n"/>
-      <c r="H51" s="134">
-        <f>IFERROR(INDIRECT("'"&amp;G51&amp;"'!E26"),"")</f>
-        <v/>
-      </c>
-      <c r="I51" s="135">
-        <f>IFERROR(INDIRECT("'"&amp;G51&amp;"'!E27"),"")</f>
-        <v/>
-      </c>
-      <c r="J51" s="136">
-        <f>IFERROR(INDIRECT("'"&amp;G51&amp;"'!E28"),"")</f>
-        <v/>
-      </c>
-      <c r="K51" s="137" t="n"/>
-      <c r="L51" s="137" t="inlineStr">
-        <is>
-          <t>In curs</t>
-        </is>
-      </c>
-      <c r="M51" s="138" t="n"/>
-    </row>
-    <row r="52" s="128">
-      <c r="B52" s="132" t="n">
-        <v>46</v>
-      </c>
-      <c r="C52" s="133" t="inlineStr">
-        <is>
-          <t>Rasnita 200 g (recipient + mecanism de macinare)</t>
-        </is>
-      </c>
-      <c r="D52" s="133" t="inlineStr">
-        <is>
-          <t>200 g</t>
-        </is>
-      </c>
-      <c r="E52" s="133" t="inlineStr">
-        <is>
-          <t>Transparent (recipient), negru (rasnita), din poza</t>
-        </is>
-      </c>
-      <c r="F52" s="133" t="inlineStr">
-        <is>
-          <t>Sare roz de Himalaya Neiodată Râșniță 200g</t>
-        </is>
-      </c>
-      <c r="G52" s="132" t="n"/>
-      <c r="H52" s="134">
-        <f>IFERROR(INDIRECT("'"&amp;G52&amp;"'!E26"),"")</f>
-        <v/>
-      </c>
-      <c r="I52" s="135">
-        <f>IFERROR(INDIRECT("'"&amp;G52&amp;"'!E27"),"")</f>
-        <v/>
-      </c>
-      <c r="J52" s="136">
-        <f>IFERROR(INDIRECT("'"&amp;G52&amp;"'!E28"),"")</f>
-        <v/>
-      </c>
-      <c r="K52" s="137" t="n"/>
-      <c r="L52" s="137" t="inlineStr">
-        <is>
-          <t>In curs</t>
-        </is>
-      </c>
-      <c r="M52" s="138" t="n"/>
-    </row>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55" ht="19.95" customHeight="1" s="128">
-      <c r="C55" s="76" t="inlineStr">
+      <c r="H48" s="132" t="n"/>
+      <c r="I48" s="132" t="n"/>
+      <c r="J48" s="132" t="n"/>
+      <c r="K48" s="132" t="n"/>
+      <c r="L48" s="132" t="n"/>
+      <c r="M48" s="132" t="n"/>
+    </row>
+    <row r="49" ht="19.95" customHeight="1" s="128">
+      <c r="C49" s="76" t="inlineStr">
         <is>
           <t>Rezumat (automat)</t>
         </is>
       </c>
-      <c r="D55" s="73" t="inlineStr">
+      <c r="D49" s="73" t="inlineStr">
         <is>
           <t>Nr. unitati</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="19.95" customHeight="1" s="128">
-      <c r="C56" s="74" t="inlineStr">
+    <row r="50" ht="19.95" customHeight="1" s="128">
+      <c r="C50" s="74" t="inlineStr">
         <is>
           <t>Unitati analizate</t>
         </is>
       </c>
-      <c r="D56" s="75">
-        <f>COUNTIF(G7:G52,"?*")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="19.95" customHeight="1" s="128">
-      <c r="C57" s="74" t="inlineStr">
+      <c r="D50" s="75">
+        <f>COUNTIF(G7:G46,"?*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="19.95" customHeight="1" s="128">
+      <c r="C51" s="74" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D57" s="75">
-        <f>COUNTIF($J$7:$J$52,C57)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="19.95" customHeight="1" s="128">
-      <c r="C58" s="74" t="inlineStr">
+      <c r="D51" s="75">
+        <f>COUNTIF($J$7:$J$46,C51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="19.95" customHeight="1" s="128">
+      <c r="C52" s="74" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D58" s="75">
-        <f>COUNTIF($J$7:$J$52,C58)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="19.95" customHeight="1" s="128">
-      <c r="C59" s="74" t="inlineStr">
+      <c r="D52" s="75">
+        <f>COUNTIF($J$7:$J$46,C52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="19.95" customHeight="1" s="128">
+      <c r="C53" s="74" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D59" s="75">
-        <f>COUNTIF($J$7:$J$52,C59)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="19.95" customHeight="1" s="128">
-      <c r="C60" s="74" t="inlineStr">
+      <c r="D53" s="75">
+        <f>COUNTIF($J$7:$J$46,C53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="19.95" customHeight="1" s="128">
+      <c r="C54" s="74" t="inlineStr">
         <is>
           <t>Sub 70% - nereciclabil</t>
         </is>
       </c>
-      <c r="D60" s="75">
-        <f>COUNTIF($J$7:$J$52,C60)</f>
+      <c r="D54" s="75">
+        <f>COUNTIF($J$7:$J$46,C54)</f>
         <v/>
       </c>
     </row>
@@ -4320,12 +4076,12 @@
     <mergeCell ref="B4:K4"/>
     <mergeCell ref="B2:K2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G7:G52">
+  <conditionalFormatting sqref="G7:G46">
     <cfRule type="expression" priority="4" dxfId="3">
       <formula>AND($G7&lt;&gt;"",$H7="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J7:J52">
+  <conditionalFormatting sqref="J7:J46">
     <cfRule type="expression" priority="1" dxfId="2">
       <formula>OR($J7="A",$J7="B")</formula>
     </cfRule>
@@ -4337,10 +4093,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="K7:K52" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Prioritate" error="Alegeti: Mare, Medie sau Mica." type="list">
+    <dataValidation sqref="K7:K46" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Prioritate" error="Alegeti: Mare, Medie sau Mica." type="list">
       <formula1>"Mare,Medie,Mica"</formula1>
     </dataValidation>
-    <dataValidation sqref="L7:L52" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Stadiu analiza" error="Valoarea nu este in lista. Puteti continua daca este intentionat." type="list" errorStyle="information">
+    <dataValidation sqref="L7:L46" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Stadiu analiza" error="Valoarea nu este in lista. Puteti continua daca este intentionat." type="list" errorStyle="information">
       <formula1>"Identificata,In completare,Completa,Oferta trimisa"</formula1>
     </dataValidation>
   </dataValidations>
